--- a/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59521</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70135</t>
+          <t>70159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65848</t>
+          <t>66105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77833</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129915</t>
+          <t>129720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145238</t>
+          <t>145325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37108</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150006</t>
+          <t>151013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166515</t>
+          <t>166811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147075</t>
+          <t>146853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163490</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302301</t>
+          <t>303408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325889</t>
+          <t>325438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41656</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50088</t>
+          <t>50539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73676</t>
+          <t>72569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63118</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77846</t>
+          <t>77738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117685</t>
+          <t>116038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137730</t>
+          <t>136685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>37493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>40062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>53055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72055</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>59848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80453</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74414</t>
+          <t>74418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120138</t>
+          <t>119224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148321</t>
+          <t>147950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70622</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90719</t>
+          <t>91227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73680</t>
+          <t>73676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92262</t>
+          <t>93763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150848</t>
+          <t>151219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179031</t>
+          <t>179945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>334656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>346730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>691673</t>
+          <t>689538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>741191</t>
+          <t>738597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136709</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169959</t>
+          <t>168703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181940</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>290717</t>
+          <t>293311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>342370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93005</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>101000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>99852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108370</t>
+          <t>108480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196316</t>
+          <t>196325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208313</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147180</t>
+          <t>147304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155839</t>
+          <t>155620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169374</t>
+          <t>170163</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182838</t>
+          <t>183080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320854</t>
+          <t>321459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>336732</t>
+          <t>337116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>31109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83581</t>
+          <t>83663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93531</t>
+          <t>93368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81298</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92778</t>
+          <t>93028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169206</t>
+          <t>168445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183949</t>
+          <t>183605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80568</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>95615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94977</t>
+          <t>94725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110687</t>
+          <t>110648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181860</t>
+          <t>182002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203068</t>
+          <t>202556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>36977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65361</t>
+          <t>65219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417091</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>439171</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>459598</t>
+          <t>461494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>485395</t>
+          <t>486339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884960</t>
+          <t>884572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>917749</t>
+          <t>918467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97997</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>131174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>91130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>99243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84304</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>93233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178990</t>
+          <t>179220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191215</t>
+          <t>191153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127560</t>
+          <t>126753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140927</t>
+          <t>140958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176804</t>
+          <t>177842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192496</t>
+          <t>192902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309483</t>
+          <t>309327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>330483</t>
+          <t>329597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57374</t>
+          <t>57530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96684</t>
+          <t>97135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114586</t>
+          <t>114362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90638</t>
+          <t>89064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106537</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192351</t>
+          <t>190344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215975</t>
+          <t>215515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>47179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>60970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84134</t>
+          <t>86141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>56179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92775</t>
+          <t>92754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>118761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>65927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84282</t>
+          <t>84661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>62483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>133349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159335</t>
+          <t>159356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365828</t>
+          <t>367557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415346</t>
+          <t>413730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448830</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>792992</t>
+          <t>791295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>837837</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>124347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>157833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122203</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155687</t>
+          <t>157303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258586</t>
+          <t>258350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>305128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31314</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66215</t>
+          <t>67211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52740</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>64014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>63458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87323</t>
+          <t>85907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114501</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>143135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95449</t>
+          <t>95285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114694</t>
+          <t>114283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95231</t>
+          <t>96647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118100</t>
+          <t>119096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197290</t>
+          <t>198718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227352</t>
+          <t>227440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67218</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97507</t>
+          <t>97443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129992</t>
+          <t>131009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106670</t>
+          <t>107863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128704</t>
+          <t>128935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141603</t>
+          <t>141940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166202</t>
+          <t>165401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256386</t>
+          <t>255369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288871</t>
+          <t>288935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81386</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69601</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113055</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123965</t>
+          <t>120899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180335</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194072</t>
+          <t>193233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230407</t>
+          <t>229382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192428</t>
+          <t>193458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235882</t>
+          <t>236865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400605</t>
+          <t>400623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456975</t>
+          <t>460041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169597</t>
+          <t>169639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>220990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>224471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>279996</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410914</t>
+          <t>409924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>491807</t>
+          <t>482981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444990</t>
+          <t>445165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496558</t>
+          <t>496516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481976</t>
+          <t>478930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534524</t>
+          <t>537501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936320</t>
+          <t>945146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017213</t>
+          <t>1018203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>72882</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>65437</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>77813</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65375</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>59444</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70159</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59497</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70227</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>75,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>72882</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>66105</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78098</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129720</t>
+          <t>129505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145325</t>
+          <t>145723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15582</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10651</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23027</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13184</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19115</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8332</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15582</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10366</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22359</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>155414</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146139</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>162676</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>159157</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>151013</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>166811</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>150990</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>166768</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>85,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>80,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>155414</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>146853</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>163230</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303408</t>
+          <t>302999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325438</t>
+          <t>325540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33317</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26055</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42592</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28089</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20435</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36233</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20478</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36256</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>15,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>33317</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>25501</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>50437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70827</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63207</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78261</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56166</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48986</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62959</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49129</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62775</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>64,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70827</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>63199</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>77738</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>68,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116038</t>
+          <t>117230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136685</t>
+          <t>137501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32434</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40054</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30313</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23520</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37493</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23704</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>37350</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32434</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25523</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>40062</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53055</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73702</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64698</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55579</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>74545</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>70031</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59848</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>80277</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60137</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>80189</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>64698</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54331</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>74418</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>120986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147950</t>
+          <t>149266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83396</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92515</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>81044</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>70798</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91227</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70886</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90938</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>83396</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>73676</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>93763</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>149903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179945</t>
+          <t>178183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>345138</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>379567</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>334656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>367316</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>333008</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>365889</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>346730</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>380608</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>689538</t>
+          <t>692115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738597</t>
+          <t>737936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>164728</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>148982</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>183411</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>152628</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>136043</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>168703</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>137470</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>164728</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>147941</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>181819</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>293972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342370</t>
+          <t>339793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>104941</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>99652</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>108245</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>98130</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93299</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>93059</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101190</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>94,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>104941</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>99852</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>108480</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196325</t>
+          <t>196584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208083</t>
+          <t>208179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12391</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5991</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10822</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11062</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3563</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>177591</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>169871</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>182825</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>152329</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>147304</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>155620</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>147748</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>155597</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>95,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>177591</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>170163</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>183080</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>321459</t>
+          <t>320556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337116</t>
+          <t>336420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15633</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23353</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7015</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12040</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3747</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15633</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10144</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88019</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81020</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93165</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89106</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83663</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93368</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>82645</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93076</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>90,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>88019</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>81434</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>93028</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168445</t>
+          <t>168402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183605</t>
+          <t>183696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13793</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8647</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20792</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8874</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14317</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15335</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>9,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13793</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8784</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>20378</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103094</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94846</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>110364</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>89374</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>80809</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>95615</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>81024</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>95413</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>77,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>103094</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>94725</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>110648</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>180757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202556</t>
+          <t>202036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28608</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21338</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36856</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>26146</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19905</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34711</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20107</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34496</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>22,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28608</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21054</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36977</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65219</t>
+          <t>66464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>460235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>484394</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>418324</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>438557</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>416621</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>438190</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>461494</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>486339</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884572</t>
+          <t>886523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>918467</t>
+          <t>919393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65136</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54387</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>78546</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>48026</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38408</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58641</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38775</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>60344</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>65136</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52442</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>77287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131174</t>
+          <t>129223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89595</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84848</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93755</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>96432</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91130</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>99243</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>91548</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>99578</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>89595</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>83713</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93233</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179220</t>
+          <t>179035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191153</t>
+          <t>191111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8672</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13419</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6272</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3461</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11574</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11156</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8672</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5034</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14554</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>185722</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>177287</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>192681</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>84,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>134680</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>126753</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>140958</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>125989</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>140817</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>86,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>185722</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>177842</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>192902</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309327</t>
+          <t>308674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>329597</t>
+          <t>329721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24870</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17911</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33305</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>21585</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15307</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29512</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15448</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30276</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24870</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>32750</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57530</t>
+          <t>58183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98213</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89692</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106047</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>105984</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97135</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>114362</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>97370</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>115263</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>98213</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>89064</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105686</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>74,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190344</t>
+          <t>191011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215515</t>
+          <t>215186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33958</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26124</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42479</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>38330</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29952</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47179</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29051</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46944</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33958</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26485</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43107</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60970</t>
+          <t>61299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86141</t>
+          <t>85474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58320</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48591</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68596</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>46545</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37445</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56179</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37361</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55176</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>58320</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49223</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67521</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>92235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118761</t>
+          <t>117315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71684</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61408</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81413</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75561</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65927</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>84661</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>66930</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>84745</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>71684</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>62483</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133349</t>
+          <t>134795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159356</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>415584</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>449887</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>367557</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>401043</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>366597</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>400140</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>413730</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>448105</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>791295</t>
+          <t>791620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>838073</t>
+          <t>840951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139183</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121146</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155449</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>141748</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>124347</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>157833</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>158793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139183</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122928</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>157303</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258350</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305128</t>
+          <t>304803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26842</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21038</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31315</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19624</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31159</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49773</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67211</t>
+          <t>56157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23695</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19222</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29499</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32126</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26352</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37887</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60684</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>46470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>60229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65113</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54480</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>75488</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53729</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45016</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>64014</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74291</t>
+          <t>51478</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63458</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85907</t>
+          <t>60541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>116590</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>102030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143135</t>
+          <t>130045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>92409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82034</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103042</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>105570</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95285</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>94040</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96647</t>
+          <t>84977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119096</t>
+          <t>102614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>213833</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198718</t>
+          <t>172994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227440</t>
+          <t>201009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59062</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70815</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55491</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44953</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66025</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>59477</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70550</t>
+          <t>70578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>118539</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97443</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131009</t>
+          <t>134503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141064</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>129311</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152583</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>118397</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107863</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128935</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>116041</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141940</t>
+          <t>104940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165401</t>
+          <t>126525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272785</t>
+          <t>257105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255369</t>
+          <t>241141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288935</t>
+          <t>274047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>72,95%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86350</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70011</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>108996</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46076</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82225</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85766</t>
+          <t>61957</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>50181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112025</t>
+          <t>74226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>148953</t>
+          <t>148307</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120899</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180317</t>
+          <t>174080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206295</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>183649</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>222634</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>212271</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>193233</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>229382</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>77,06%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>219717</t>
+          <t>194596</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>182327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236865</t>
+          <t>206372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>431987</t>
+          <t>400891</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400623</t>
+          <t>375118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460041</t>
+          <t>423098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214504</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>264437</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>169639</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>220990</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224471</t>
+          <t>176518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>214951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409924</t>
+          <t>400997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482981</t>
+          <t>461688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>463463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>436392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>486325</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,13%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>468363</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>445165</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>496516</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>510927</t>
+          <t>434697</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>414727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537501</t>
+          <t>453160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>979290</t>
+          <t>898160</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>945146</t>
+          <t>868820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1018203</t>
+          <t>929511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
